--- a/Template_Rekapitulasi_Kehadiran_FHISIP_Resmi.xlsx
+++ b/Template_Rekapitulasi_Kehadiran_FHISIP_Resmi.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Rekap " sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rekap '!$A$1:$AJ$209</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Rekap '!$A$1:$AJ$210</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Rekap '!$10:$11</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="183">
   <si>
     <t>Laporan Rekapitulasi</t>
   </si>
@@ -590,7 +590,10 @@
     <t>Firya Syafira, S.Kom.</t>
   </si>
   <si>
-    <t>Grand Total: 135</t>
+    <t>SRI SEDIAN</t>
+  </si>
+  <si>
+    <t>Grand Total: 136</t>
   </si>
   <si>
     <t>Oleh:</t>
@@ -1928,7 +1931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL209"/>
+  <dimension ref="A1:AL210"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="0.25" style="1" customWidth="1"/>
@@ -11533,27 +11536,31 @@
       </c>
     </row>
     <row r="195" spans="2:37" ht="16.35" customHeight="1">
-      <c r="B195" s="80" t="s">
-        <v>31</v>
-      </c>
-      <c r="C195" s="81"/>
-      <c r="D195" s="81"/>
-      <c r="E195" s="81"/>
-      <c r="F195" s="81"/>
-      <c r="G195" s="81"/>
-      <c r="H195" s="81"/>
-      <c r="I195" s="81"/>
-      <c r="J195" s="82"/>
+      <c r="B195" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="C195" s="74"/>
+      <c r="D195" s="74"/>
+      <c r="E195" s="74"/>
+      <c r="F195" s="74"/>
+      <c r="G195" s="73">
+        <v>586</v>
+      </c>
+      <c r="H195" s="74"/>
+      <c r="I195" s="74"/>
+      <c r="J195" s="74"/>
       <c r="K195" s="17">
-        <f>SUM(K188:K194)</f>
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="L195" s="18">
-        <f>SUM(L188:L194)</f>
-        <v>147</v>
-      </c>
-      <c r="M195" s="75"/>
-      <c r="N195" s="83"/>
+        <f>K195-M195</f>
+        <v>21</v>
+      </c>
+      <c r="M195" s="75">
+        <f>S195+T195+Z195+AA195+AC195</f>
+        <v>0</v>
+      </c>
+      <c r="N195" s="76"/>
       <c r="O195" s="19"/>
       <c r="P195" s="75"/>
       <c r="Q195" s="83"/>
@@ -11569,19 +11576,22 @@
       <c r="AA195" s="77"/>
       <c r="AB195" s="84"/>
       <c r="AC195" s="19"/>
-      <c r="AD195" s="77">
-        <f>SUM(AD188:AE194)</f>
-        <v>147</v>
-      </c>
-      <c r="AE195" s="84"/>
+      <c r="AD195" s="89">
+        <f>K195-M195</f>
+        <v>21</v>
+      </c>
+      <c r="AE195" s="91"/>
       <c r="AF195" s="20"/>
       <c r="AG195" s="20"/>
       <c r="AH195" s="78"/>
       <c r="AI195" s="79"/>
-    </row>
-    <row r="196" spans="2:38" ht="16.35" customHeight="1">
+      <c r="AK195" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="2:37" ht="16.35" customHeight="1">
       <c r="B196" s="80" t="s">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="C196" s="81"/>
       <c r="D196" s="81"/>
@@ -11592,12 +11602,12 @@
       <c r="I196" s="81"/>
       <c r="J196" s="82"/>
       <c r="K196" s="17">
-        <f>SUM(K20,K46,K50,K54,K57,K67,K71,K82,K85,K91,K96,K105,K108,K119,K122,K131,K134,K138,K148,K168,K180,K183,K186,K195)</f>
-        <v>2835</v>
+        <f>SUM(K188:K195)</f>
+        <v>168</v>
       </c>
       <c r="L196" s="18">
-        <f>SUM(L20,L46,L50,L54,L57,L67,L71,L82,L85,L91,L96,L105,L108,L119,L122,L131,L134,L138,L148,L168,L180,L183,L186,L195)</f>
-        <v>2835</v>
+        <f>SUM(L188:L195)</f>
+        <v>168</v>
       </c>
       <c r="M196" s="75"/>
       <c r="N196" s="83"/>
@@ -11617,75 +11627,106 @@
       <c r="AB196" s="84"/>
       <c r="AC196" s="19"/>
       <c r="AD196" s="77">
-        <f>SUM(AD20,AD46,AD50,AD54,AD57,AD67,AD71,AD82,AD85,AD91,AD96,AD105,AD108,AD119,AD122,AD131,AD134,AD138,AD148,AD168,AD180,AD183,AD186,AD195)</f>
-        <v>2835</v>
+        <f>SUM(AD188:AE195)</f>
+        <v>168</v>
       </c>
       <c r="AE196" s="84"/>
-      <c r="AF196" s="19"/>
-      <c r="AG196" s="19"/>
-      <c r="AH196" s="77"/>
-      <c r="AI196" s="84"/>
-      <c r="AK196" s="1">
-        <f>SUM(AK13:AK195)</f>
-        <v>135</v>
-      </c>
-    </row>
-    <row r="197" spans="2:38" ht="0.75" customHeight="1">
-      <c r="L197" s="43"/>
-    </row>
-    <row r="198" spans="2:38" ht="2.25" customHeight="1">
+      <c r="AF196" s="20"/>
+      <c r="AG196" s="20"/>
+      <c r="AH196" s="78"/>
+      <c r="AI196" s="79"/>
+    </row>
+    <row r="197" spans="2:38" ht="16.35" customHeight="1">
+      <c r="B197" s="80" t="s">
+        <v>174</v>
+      </c>
+      <c r="C197" s="81"/>
+      <c r="D197" s="81"/>
+      <c r="E197" s="81"/>
+      <c r="F197" s="81"/>
+      <c r="G197" s="81"/>
+      <c r="H197" s="81"/>
+      <c r="I197" s="81"/>
+      <c r="J197" s="82"/>
+      <c r="K197" s="17">
+        <f>SUM(K20,K46,K50,K54,K57,K67,K71,K82,K85,K91,K96,K105,K108,K119,K122,K131,K134,K138,K148,K168,K180,K183,K186,K196)</f>
+        <v>2856</v>
+      </c>
+      <c r="L197" s="18">
+        <f>SUM(L20,L46,L50,L54,L57,L67,L71,L82,L85,L91,L96,L105,L108,L119,L122,L131,L134,L138,L148,L168,L180,L183,L186,L196)</f>
+        <v>2856</v>
+      </c>
+      <c r="M197" s="75"/>
+      <c r="N197" s="83"/>
+      <c r="O197" s="19"/>
+      <c r="P197" s="75"/>
+      <c r="Q197" s="83"/>
+      <c r="R197" s="17"/>
+      <c r="S197" s="17"/>
+      <c r="T197" s="77"/>
+      <c r="U197" s="83"/>
+      <c r="V197" s="84"/>
+      <c r="W197" s="19"/>
+      <c r="X197" s="19"/>
+      <c r="Y197" s="19"/>
+      <c r="Z197" s="19"/>
+      <c r="AA197" s="77"/>
+      <c r="AB197" s="84"/>
+      <c r="AC197" s="19"/>
+      <c r="AD197" s="77">
+        <f>SUM(AD20,AD46,AD50,AD54,AD57,AD67,AD71,AD82,AD85,AD91,AD96,AD105,AD108,AD119,AD122,AD131,AD134,AD138,AD148,AD168,AD180,AD183,AD186,AD196)</f>
+        <v>2856</v>
+      </c>
+      <c r="AE197" s="84"/>
+      <c r="AF197" s="19"/>
+      <c r="AG197" s="19"/>
+      <c r="AH197" s="77"/>
+      <c r="AI197" s="84"/>
+      <c r="AK197" s="1">
+        <f>SUM(AK13:AK196)</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="198" spans="2:38" ht="0.75" customHeight="1">
       <c r="L198" s="43"/>
     </row>
-    <row r="199" spans="2:38" ht="10.7" customHeight="1">
-      <c r="C199" s="56" t="s">
-        <v>174</v>
-      </c>
-      <c r="E199" s="56" t="s">
+    <row r="199" spans="2:38" ht="2.25" customHeight="1">
+      <c r="L199" s="43"/>
+    </row>
+    <row r="200" spans="2:38" ht="10.7" customHeight="1">
+      <c r="C200" s="56" t="s">
         <v>175</v>
       </c>
-      <c r="F199" s="54"/>
-      <c r="G199" s="54"/>
-      <c r="H199" s="54"/>
-      <c r="J199" s="53" t="s">
+      <c r="E200" s="56" t="s">
         <v>176</v>
       </c>
-      <c r="K199" s="54"/>
-      <c r="L199" s="55"/>
-      <c r="M199" s="54"/>
-      <c r="AE199" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="AF199" s="62"/>
-      <c r="AG199" s="62"/>
-      <c r="AH199" s="62"/>
-    </row>
-    <row r="200" spans="2:38" ht="3" customHeight="1">
-      <c r="C200" s="54"/>
-      <c r="E200" s="54"/>
       <c r="F200" s="54"/>
       <c r="G200" s="54"/>
       <c r="H200" s="54"/>
-      <c r="L200" s="43"/>
-      <c r="AE200" s="62"/>
+      <c r="J200" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="K200" s="54"/>
+      <c r="L200" s="55"/>
+      <c r="M200" s="54"/>
+      <c r="AE200" s="61" t="s">
+        <v>178</v>
+      </c>
       <c r="AF200" s="62"/>
       <c r="AG200" s="62"/>
       <c r="AH200" s="62"/>
     </row>
-    <row r="202" spans="2:38" ht="15">
-      <c r="L202" s="43"/>
-      <c r="S202" s="39"/>
-      <c r="T202" s="39"/>
-      <c r="U202" s="39"/>
-      <c r="V202" s="39"/>
-      <c r="W202" s="39"/>
-      <c r="X202" s="39"/>
-      <c r="Y202" s="40"/>
-      <c r="Z202" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA202" s="39"/>
-      <c r="AB202" s="39"/>
-      <c r="AC202" s="39"/>
+    <row r="201" spans="2:38" ht="3" customHeight="1">
+      <c r="C201" s="54"/>
+      <c r="E201" s="54"/>
+      <c r="F201" s="54"/>
+      <c r="G201" s="54"/>
+      <c r="H201" s="54"/>
+      <c r="L201" s="43"/>
+      <c r="AE201" s="62"/>
+      <c r="AF201" s="62"/>
+      <c r="AG201" s="62"/>
+      <c r="AH201" s="62"/>
     </row>
     <row r="203" spans="2:38" ht="15">
       <c r="L203" s="43"/>
@@ -11711,8 +11752,10 @@
       <c r="V204" s="39"/>
       <c r="W204" s="39"/>
       <c r="X204" s="39"/>
-      <c r="Y204" s="39"/>
-      <c r="Z204" s="41"/>
+      <c r="Y204" s="40"/>
+      <c r="Z204" s="41" t="s">
+        <v>180</v>
+      </c>
       <c r="AA204" s="39"/>
       <c r="AB204" s="39"/>
       <c r="AC204" s="39"/>
@@ -11731,7 +11774,8 @@
       <c r="AB205" s="39"/>
       <c r="AC205" s="39"/>
     </row>
-    <row r="206" spans="19:29" ht="15">
+    <row r="206" spans="2:38" ht="15">
+      <c r="L206" s="43"/>
       <c r="S206" s="39"/>
       <c r="T206" s="39"/>
       <c r="U206" s="39"/>
@@ -11752,7 +11796,7 @@
       <c r="W207" s="39"/>
       <c r="X207" s="39"/>
       <c r="Y207" s="39"/>
-      <c r="Z207" s="42"/>
+      <c r="Z207" s="41"/>
       <c r="AA207" s="39"/>
       <c r="AB207" s="39"/>
       <c r="AC207" s="39"/>
@@ -11764,10 +11808,8 @@
       <c r="V208" s="39"/>
       <c r="W208" s="39"/>
       <c r="X208" s="39"/>
-      <c r="Y208" s="40"/>
-      <c r="Z208" s="41" t="s">
-        <v>180</v>
-      </c>
+      <c r="Y208" s="39"/>
+      <c r="Z208" s="42"/>
       <c r="AA208" s="39"/>
       <c r="AB208" s="39"/>
       <c r="AC208" s="39"/>
@@ -11787,8 +11829,23 @@
       <c r="AB209" s="39"/>
       <c r="AC209" s="39"/>
     </row>
+    <row r="210" spans="19:29" ht="15">
+      <c r="S210" s="39"/>
+      <c r="T210" s="39"/>
+      <c r="U210" s="39"/>
+      <c r="V210" s="39"/>
+      <c r="W210" s="39"/>
+      <c r="X210" s="39"/>
+      <c r="Y210" s="40"/>
+      <c r="Z210" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA210" s="39"/>
+      <c r="AB210" s="39"/>
+      <c r="AC210" s="39"/>
+    </row>
   </sheetData>
-  <mergeCells count="1300">
+  <mergeCells count="1308">
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="P10:Q10"/>
     <mergeCell ref="T10:V10"/>
@@ -13068,7 +13125,8 @@
     <mergeCell ref="AA194:AB194"/>
     <mergeCell ref="AD194:AE194"/>
     <mergeCell ref="AH194:AI194"/>
-    <mergeCell ref="B195:J195"/>
+    <mergeCell ref="B195:F195"/>
+    <mergeCell ref="G195:J195"/>
     <mergeCell ref="M195:N195"/>
     <mergeCell ref="P195:Q195"/>
     <mergeCell ref="T195:V195"/>
@@ -13082,13 +13140,20 @@
     <mergeCell ref="AA196:AB196"/>
     <mergeCell ref="AD196:AE196"/>
     <mergeCell ref="AH196:AI196"/>
+    <mergeCell ref="B197:J197"/>
+    <mergeCell ref="M197:N197"/>
+    <mergeCell ref="P197:Q197"/>
+    <mergeCell ref="T197:V197"/>
+    <mergeCell ref="AA197:AB197"/>
+    <mergeCell ref="AD197:AE197"/>
+    <mergeCell ref="AH197:AI197"/>
     <mergeCell ref="A1:P3"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="AB3:AH8"/>
-    <mergeCell ref="J199:M199"/>
-    <mergeCell ref="C199:C200"/>
-    <mergeCell ref="E199:H200"/>
-    <mergeCell ref="AE199:AH200"/>
+    <mergeCell ref="J200:M200"/>
+    <mergeCell ref="C200:C201"/>
+    <mergeCell ref="E200:H201"/>
+    <mergeCell ref="AE200:AH201"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="109" fitToHeight="0" orientation="landscape"/>
